--- a/results/sequences.xlsx
+++ b/results/sequences.xlsx
@@ -54,7 +54,7 @@
     <t>2026-03-17 12:59:45</t>
   </si>
   <si>
-    <t>127:20:34</t>
+    <t>127:57:16</t>
   </si>
   <si>
     <t>KA6137MT</t>
@@ -78,7 +78,7 @@
     <t>2026-03-17 13:01:20</t>
   </si>
   <si>
-    <t>127:18:59</t>
+    <t>127:55:41</t>
   </si>
   <si>
     <t>KA8611PK</t>
@@ -159,7 +159,7 @@
     <t>2026-03-17 13:42:14</t>
   </si>
   <si>
-    <t>126:38:05</t>
+    <t>127:14:47</t>
   </si>
   <si>
     <t>AI2018YB</t>
@@ -168,7 +168,7 @@
     <t>2026-03-17 13:14:59</t>
   </si>
   <si>
-    <t>127:05:20</t>
+    <t>127:42:02</t>
   </si>
   <si>
     <t>AI2010E</t>
@@ -177,7 +177,7 @@
     <t>2026-03-17 13:15:04</t>
   </si>
   <si>
-    <t>127:05:15</t>
+    <t>127:41:57</t>
   </si>
   <si>
     <t>KA0993MP</t>
@@ -210,7 +210,7 @@
     <t>2026-03-18 15:52:20</t>
   </si>
   <si>
-    <t>100:27:59</t>
+    <t>101:04:41</t>
   </si>
   <si>
     <t>KA0993M</t>
@@ -237,7 +237,7 @@
     <t>2026-03-17 14:37:10</t>
   </si>
   <si>
-    <t>125:43:09</t>
+    <t>126:19:51</t>
   </si>
   <si>
     <t>KA0082X</t>
@@ -303,7 +303,7 @@
     <t>2026-03-17 16:21:01</t>
   </si>
   <si>
-    <t>123:59:17</t>
+    <t>124:35:59</t>
   </si>
   <si>
     <t>KA8176TB</t>
@@ -324,7 +324,7 @@
     <t>2026-03-17 14:07:18</t>
   </si>
   <si>
-    <t>126:13:01</t>
+    <t>126:49:43</t>
   </si>
   <si>
     <t>AA1552OK</t>
@@ -333,7 +333,7 @@
     <t>2026-03-17 13:54:03</t>
   </si>
   <si>
-    <t>126:26:16</t>
+    <t>127:02:58</t>
   </si>
   <si>
     <t>AA8365BC</t>
@@ -342,7 +342,7 @@
     <t>2026-03-17 14:22:03</t>
   </si>
   <si>
-    <t>125:58:16</t>
+    <t>126:34:58</t>
   </si>
   <si>
     <t>KA8820IA</t>
@@ -351,7 +351,7 @@
     <t>2026-03-17 14:10:24</t>
   </si>
   <si>
-    <t>126:09:55</t>
+    <t>126:46:37</t>
   </si>
   <si>
     <t>A8186EB</t>
@@ -360,7 +360,7 @@
     <t>2026-03-17 14:29:53</t>
   </si>
   <si>
-    <t>125:50:26</t>
+    <t>126:27:08</t>
   </si>
   <si>
     <t>AI8888OX</t>
@@ -369,7 +369,7 @@
     <t>2026-03-17 15:24:02</t>
   </si>
   <si>
-    <t>124:56:17</t>
+    <t>125:32:59</t>
   </si>
   <si>
     <t>KA7368PT</t>
@@ -393,7 +393,7 @@
     <t>2026-03-18 16:26:06</t>
   </si>
   <si>
-    <t>99:54:12</t>
+    <t>100:30:55</t>
   </si>
   <si>
     <t>KA0732MT</t>
@@ -450,7 +450,7 @@
     <t>2026-03-18 12:34:35</t>
   </si>
   <si>
-    <t>103:45:44</t>
+    <t>104:22:26</t>
   </si>
   <si>
     <t>KA7945EE</t>
@@ -459,7 +459,7 @@
     <t>2026-03-17 14:58:04</t>
   </si>
   <si>
-    <t>125:22:15</t>
+    <t>125:58:57</t>
   </si>
   <si>
     <t>KA7361PT</t>
@@ -474,7 +474,7 @@
     <t>00:01:30</t>
   </si>
   <si>
-    <t>125:20:05</t>
+    <t>125:56:47</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA7361PT</t>
@@ -519,7 +519,7 @@
     <t>2026-03-18 14:17:52</t>
   </si>
   <si>
-    <t>102:02:27</t>
+    <t>102:39:09</t>
   </si>
   <si>
     <t>KA6274EX</t>
@@ -528,7 +528,7 @@
     <t>2026-03-17 15:05:11</t>
   </si>
   <si>
-    <t>125:15:08</t>
+    <t>125:51:50</t>
   </si>
   <si>
     <t>KA0068BI</t>
@@ -537,7 +537,7 @@
     <t>2026-03-17 15:52:14</t>
   </si>
   <si>
-    <t>124:28:05</t>
+    <t>125:04:47</t>
   </si>
   <si>
     <t>KA1100CT</t>
@@ -561,7 +561,7 @@
     <t>2026-03-19 13:58:22</t>
   </si>
   <si>
-    <t>78:21:57</t>
+    <t>78:58:39</t>
   </si>
   <si>
     <t>KA0178TB</t>
@@ -576,7 +576,7 @@
     <t>2026-03-17 15:42:56</t>
   </si>
   <si>
-    <t>124:37:23</t>
+    <t>125:14:05</t>
   </si>
   <si>
     <t>2026-03-17 15:52:19</t>
@@ -612,7 +612,7 @@
     <t>2026-03-19 11:38:00</t>
   </si>
   <si>
-    <t>80:42:19</t>
+    <t>81:19:01</t>
   </si>
   <si>
     <t>KA0008OT</t>
@@ -621,7 +621,7 @@
     <t>2026-03-17 16:22:18</t>
   </si>
   <si>
-    <t>123:58:00</t>
+    <t>124:34:42</t>
   </si>
   <si>
     <t>AA3279OK</t>
@@ -630,7 +630,7 @@
     <t>2026-03-17 16:20:25</t>
   </si>
   <si>
-    <t>123:59:54</t>
+    <t>124:36:36</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: AA3279OK</t>
@@ -642,7 +642,7 @@
     <t>2026-03-17 16:44:28</t>
   </si>
   <si>
-    <t>123:35:51</t>
+    <t>124:12:33</t>
   </si>
   <si>
     <t>2026-03-17 16:44:33</t>
@@ -660,7 +660,7 @@
     <t>2026-03-17 17:57:14</t>
   </si>
   <si>
-    <t>122:23:05</t>
+    <t>122:59:47</t>
   </si>
   <si>
     <t>KA7458PT</t>
@@ -756,7 +756,7 @@
     <t>2026-03-17 17:37:10</t>
   </si>
   <si>
-    <t>122:43:08</t>
+    <t>123:19:50</t>
   </si>
   <si>
     <t>KA9990BH</t>
@@ -774,7 +774,7 @@
     <t>00:00:58</t>
   </si>
   <si>
-    <t>122:24:12</t>
+    <t>123:00:54</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA9990BH</t>
@@ -786,7 +786,7 @@
     <t>2026-03-17 17:55:07</t>
   </si>
   <si>
-    <t>122:25:12</t>
+    <t>123:01:54</t>
   </si>
   <si>
     <t>AA8845BO</t>
@@ -795,7 +795,7 @@
     <t>2026-03-17 17:57:18</t>
   </si>
   <si>
-    <t>122:23:01</t>
+    <t>122:59:43</t>
   </si>
   <si>
     <t>KA9158HO</t>
@@ -804,7 +804,7 @@
     <t>2026-03-18 08:37:24</t>
   </si>
   <si>
-    <t>107:42:55</t>
+    <t>108:19:37</t>
   </si>
   <si>
     <t>AA3163YC</t>
@@ -846,7 +846,7 @@
     <t>2026-03-18 15:57:57</t>
   </si>
   <si>
-    <t>100:22:22</t>
+    <t>100:59:04</t>
   </si>
   <si>
     <t>KA7828BB</t>
@@ -915,7 +915,7 @@
     <t>2026-03-20 13:20:37</t>
   </si>
   <si>
-    <t>54:59:42</t>
+    <t>55:36:24</t>
   </si>
   <si>
     <t>A7828BB</t>
@@ -924,7 +924,7 @@
     <t>2026-03-18 09:12:18</t>
   </si>
   <si>
-    <t>107:08:01</t>
+    <t>107:44:43</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: A7828BB</t>
@@ -1008,7 +1008,7 @@
     <t>2026-03-18 09:37:58</t>
   </si>
   <si>
-    <t>106:42:21</t>
+    <t>107:19:03</t>
   </si>
   <si>
     <t>HH9726AC</t>
@@ -1053,7 +1053,7 @@
     <t>2026-03-19 09:46:22</t>
   </si>
   <si>
-    <t>82:33:57</t>
+    <t>83:10:39</t>
   </si>
   <si>
     <t>KA0087BK</t>
@@ -1062,7 +1062,7 @@
     <t>2026-03-18 10:45:22</t>
   </si>
   <si>
-    <t>105:34:57</t>
+    <t>106:11:39</t>
   </si>
   <si>
     <t>0037BK</t>
@@ -1071,7 +1071,7 @@
     <t>2026-03-18 10:16:48</t>
   </si>
   <si>
-    <t>106:03:31</t>
+    <t>106:40:13</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: 0037BK</t>
@@ -1083,7 +1083,7 @@
     <t>2026-03-18 10:44:10</t>
   </si>
   <si>
-    <t>105:36:09</t>
+    <t>106:12:51</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA0623MI</t>
@@ -1095,7 +1095,7 @@
     <t>2026-03-18 10:43:13</t>
   </si>
   <si>
-    <t>105:37:05</t>
+    <t>106:13:48</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: 9726AC</t>
@@ -1107,7 +1107,7 @@
     <t>2026-03-18 10:44:43</t>
   </si>
   <si>
-    <t>105:35:36</t>
+    <t>106:12:18</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: 7726AC</t>
@@ -1143,7 +1143,7 @@
     <t>2026-03-18 10:55:44</t>
   </si>
   <si>
-    <t>105:24:35</t>
+    <t>106:01:17</t>
   </si>
   <si>
     <t>KA4511P</t>
@@ -1152,7 +1152,7 @@
     <t>2026-03-18 11:31:20</t>
   </si>
   <si>
-    <t>104:48:59</t>
+    <t>105:25:41</t>
   </si>
   <si>
     <t>KA4415ME</t>
@@ -1179,7 +1179,7 @@
     <t>2026-03-18 16:30:41</t>
   </si>
   <si>
-    <t>99:49:37</t>
+    <t>100:26:19</t>
   </si>
   <si>
     <t>BM1401CH</t>
@@ -1188,7 +1188,7 @@
     <t>2026-03-18 11:57:18</t>
   </si>
   <si>
-    <t>104:23:01</t>
+    <t>104:59:43</t>
   </si>
   <si>
     <t>AE0022MX</t>
@@ -1212,13 +1212,13 @@
     <t>2026-03-18 15:06:35</t>
   </si>
   <si>
-    <t>101:13:44</t>
+    <t>101:50:26</t>
   </si>
   <si>
     <t>2026-03-18 12:50:22</t>
   </si>
   <si>
-    <t>103:29:56</t>
+    <t>104:06:38</t>
   </si>
   <si>
     <t>KA008K</t>
@@ -1227,7 +1227,7 @@
     <t>2026-03-18 12:12:59</t>
   </si>
   <si>
-    <t>104:07:20</t>
+    <t>104:44:02</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: KA008K</t>
@@ -1269,7 +1269,7 @@
     <t>2026-03-19 13:18:16</t>
   </si>
   <si>
-    <t>79:02:03</t>
+    <t>79:38:45</t>
   </si>
   <si>
     <t>KA6050PH</t>
@@ -1278,7 +1278,7 @@
     <t>2026-03-18 17:43:49</t>
   </si>
   <si>
-    <t>98:36:30</t>
+    <t>99:13:12</t>
   </si>
   <si>
     <t>KA9911AO</t>
@@ -1305,7 +1305,7 @@
     <t>2026-03-18 14:00:03</t>
   </si>
   <si>
-    <t>102:20:16</t>
+    <t>102:56:58</t>
   </si>
   <si>
     <t>KA9911A</t>
@@ -1323,7 +1323,7 @@
     <t>2026-03-18 13:19:22</t>
   </si>
   <si>
-    <t>103:00:57</t>
+    <t>103:37:39</t>
   </si>
   <si>
     <t>BK8888TP</t>
@@ -1389,7 +1389,7 @@
     <t>2026-03-19 19:36:38</t>
   </si>
   <si>
-    <t>72:43:41</t>
+    <t>73:20:23</t>
   </si>
   <si>
     <t>KA6550TB</t>
@@ -1404,7 +1404,7 @@
     <t>2026-03-18 14:22:21</t>
   </si>
   <si>
-    <t>101:57:58</t>
+    <t>102:34:40</t>
   </si>
   <si>
     <t>KA7509T</t>
@@ -1521,7 +1521,7 @@
     <t>2026-03-18 15:31:40</t>
   </si>
   <si>
-    <t>100:48:39</t>
+    <t>101:25:21</t>
   </si>
   <si>
     <t>CA7272BB</t>
@@ -1530,7 +1530,7 @@
     <t>2026-03-18 15:44:07</t>
   </si>
   <si>
-    <t>100:36:12</t>
+    <t>101:12:54</t>
   </si>
   <si>
     <t>1163KK</t>
@@ -1578,7 +1578,7 @@
     <t>2026-03-19 15:20:06</t>
   </si>
   <si>
-    <t>77:00:13</t>
+    <t>77:36:55</t>
   </si>
   <si>
     <t>KA4444C</t>
@@ -1668,7 +1668,7 @@
     <t>02:14:13</t>
   </si>
   <si>
-    <t>03:10:40</t>
+    <t>03:47:22</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: KA8390PI</t>
@@ -1686,7 +1686,7 @@
     <t>2026-03-19 11:17:18</t>
   </si>
   <si>
-    <t>81:03:01</t>
+    <t>81:39:43</t>
   </si>
   <si>
     <t>KA9336ME</t>
@@ -1719,7 +1719,7 @@
     <t>2026-03-20 18:54:10</t>
   </si>
   <si>
-    <t>49:26:09</t>
+    <t>50:02:51</t>
   </si>
   <si>
     <t>KA603H</t>
@@ -1728,7 +1728,7 @@
     <t>2026-03-18 17:44:29</t>
   </si>
   <si>
-    <t>98:35:50</t>
+    <t>99:12:32</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA603H</t>
@@ -1740,7 +1740,7 @@
     <t>2026-03-18 17:44:30</t>
   </si>
   <si>
-    <t>98:35:49</t>
+    <t>99:12:31</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA6050H</t>
@@ -1752,7 +1752,7 @@
     <t>2026-03-18 17:52:03</t>
   </si>
   <si>
-    <t>98:28:15</t>
+    <t>99:04:57</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: 7726AO</t>
@@ -1818,7 +1818,7 @@
     <t>2026-03-21 12:54:02</t>
   </si>
   <si>
-    <t>31:26:17</t>
+    <t>32:02:59</t>
   </si>
   <si>
     <t>2026-03-18 18:21:30</t>
@@ -1875,7 +1875,7 @@
     <t>00:45:29</t>
   </si>
   <si>
-    <t>03:32:18</t>
+    <t>04:09:00</t>
   </si>
   <si>
     <t>2026-03-22 16:48:52</t>
@@ -1887,7 +1887,7 @@
     <t>2026-03-18 18:42:41</t>
   </si>
   <si>
-    <t>97:37:38</t>
+    <t>98:14:20</t>
   </si>
   <si>
     <t>AB2050HI</t>
@@ -1896,7 +1896,7 @@
     <t>2026-03-19 09:20:51</t>
   </si>
   <si>
-    <t>82:59:28</t>
+    <t>83:36:10</t>
   </si>
   <si>
     <t>B2450HI</t>
@@ -1905,7 +1905,7 @@
     <t>2026-03-19 08:54:11</t>
   </si>
   <si>
-    <t>83:26:08</t>
+    <t>84:02:50</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: B2450HI</t>
@@ -1917,7 +1917,7 @@
     <t>2026-03-19 09:12:32</t>
   </si>
   <si>
-    <t>83:07:47</t>
+    <t>83:44:29</t>
   </si>
   <si>
     <t>AA0009MH</t>
@@ -1941,7 +1941,7 @@
     <t>2026-03-19 17:27:57</t>
   </si>
   <si>
-    <t>74:52:22</t>
+    <t>75:29:04</t>
   </si>
   <si>
     <t>BK0542KA</t>
@@ -1977,7 +1977,7 @@
     <t>2026-03-21 14:44:32</t>
   </si>
   <si>
-    <t>29:35:46</t>
+    <t>30:12:28</t>
   </si>
   <si>
     <t>AI0468BP</t>
@@ -1986,7 +1986,7 @@
     <t>2026-03-19 09:25:19</t>
   </si>
   <si>
-    <t>82:55:00</t>
+    <t>83:31:42</t>
   </si>
   <si>
     <t>AA0011KB</t>
@@ -2013,7 +2013,7 @@
     <t>2026-03-19 16:35:08</t>
   </si>
   <si>
-    <t>75:45:11</t>
+    <t>76:21:53</t>
   </si>
   <si>
     <t>BH7295TI</t>
@@ -2061,7 +2061,7 @@
     <t>2026-03-19 17:26:43</t>
   </si>
   <si>
-    <t>74:53:36</t>
+    <t>75:30:18</t>
   </si>
   <si>
     <t>BBH7295T</t>
@@ -2076,7 +2076,7 @@
     <t>2026-03-19 10:06:30</t>
   </si>
   <si>
-    <t>82:13:49</t>
+    <t>82:50:31</t>
   </si>
   <si>
     <t>0542KA</t>
@@ -2145,7 +2145,7 @@
     <t>2026-03-19 14:13:25</t>
   </si>
   <si>
-    <t>78:06:54</t>
+    <t>78:43:36</t>
   </si>
   <si>
     <t>BA7777TA</t>
@@ -2154,7 +2154,7 @@
     <t>2026-03-19 10:55:53</t>
   </si>
   <si>
-    <t>81:24:26</t>
+    <t>82:01:08</t>
   </si>
   <si>
     <t>KA1211AO</t>
@@ -2181,7 +2181,7 @@
     <t>2026-03-19 13:37:54</t>
   </si>
   <si>
-    <t>78:42:25</t>
+    <t>79:19:07</t>
   </si>
   <si>
     <t>2026-03-19 10:47:40</t>
@@ -2190,7 +2190,7 @@
     <t>2026-03-19 11:05:34</t>
   </si>
   <si>
-    <t>81:14:45</t>
+    <t>81:51:27</t>
   </si>
   <si>
     <t>KA0701CO</t>
@@ -2217,7 +2217,7 @@
     <t>2026-03-19 14:50:19</t>
   </si>
   <si>
-    <t>77:30:00</t>
+    <t>78:06:42</t>
   </si>
   <si>
     <t>6050PH</t>
@@ -2259,7 +2259,7 @@
     <t>2026-03-19 11:00:48</t>
   </si>
   <si>
-    <t>81:19:31</t>
+    <t>81:56:13</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: BA7777TH</t>
@@ -2307,7 +2307,7 @@
     <t>2026-03-20 17:28:35</t>
   </si>
   <si>
-    <t>50:51:44</t>
+    <t>51:28:26</t>
   </si>
   <si>
     <t>KA8116MC</t>
@@ -2331,7 +2331,7 @@
     <t>2026-03-19 17:14:58</t>
   </si>
   <si>
-    <t>75:05:21</t>
+    <t>75:42:03</t>
   </si>
   <si>
     <t>KA0007TP</t>
@@ -2349,7 +2349,7 @@
     <t>2026-03-20 15:46:37</t>
   </si>
   <si>
-    <t>52:33:42</t>
+    <t>53:10:24</t>
   </si>
   <si>
     <t>KA1007T</t>
@@ -2358,7 +2358,7 @@
     <t>2026-03-19 11:48:51</t>
   </si>
   <si>
-    <t>80:31:28</t>
+    <t>81:08:10</t>
   </si>
   <si>
     <t>16BP2782</t>
@@ -2388,7 +2388,7 @@
     <t>2026-03-19 17:14:19</t>
   </si>
   <si>
-    <t>75:06:00</t>
+    <t>75:42:42</t>
   </si>
   <si>
     <t>AE253H</t>
@@ -2418,7 +2418,7 @@
     <t>2026-03-19 13:05:20</t>
   </si>
   <si>
-    <t>79:14:59</t>
+    <t>79:51:41</t>
   </si>
   <si>
     <t>KA3739PI</t>
@@ -2448,7 +2448,7 @@
     <t>2026-03-20 10:21:43</t>
   </si>
   <si>
-    <t>57:58:36</t>
+    <t>58:35:18</t>
   </si>
   <si>
     <t>H7295TI</t>
@@ -2469,7 +2469,7 @@
     <t>2026-03-19 14:02:08</t>
   </si>
   <si>
-    <t>78:18:11</t>
+    <t>78:54:53</t>
   </si>
   <si>
     <t>AA0004P</t>
@@ -2505,7 +2505,7 @@
     <t>2026-03-20 09:06:06</t>
   </si>
   <si>
-    <t>59:14:13</t>
+    <t>59:50:55</t>
   </si>
   <si>
     <t>BH7777TA</t>
@@ -2556,7 +2556,7 @@
     <t>2026-03-19 18:14:13</t>
   </si>
   <si>
-    <t>74:06:06</t>
+    <t>74:42:48</t>
   </si>
   <si>
     <t>K5555XP</t>
@@ -2565,7 +2565,7 @@
     <t>2026-03-19 14:14:23</t>
   </si>
   <si>
-    <t>78:05:56</t>
+    <t>78:42:38</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: K5555XP</t>
@@ -2574,7 +2574,7 @@
     <t>2026-03-19 14:23:14</t>
   </si>
   <si>
-    <t>77:57:05</t>
+    <t>78:33:47</t>
   </si>
   <si>
     <t>AA0004PO</t>
@@ -2610,7 +2610,7 @@
     <t>2026-03-20 09:06:16</t>
   </si>
   <si>
-    <t>59:14:03</t>
+    <t>59:50:45</t>
   </si>
   <si>
     <t>KA0701C</t>
@@ -2664,7 +2664,7 @@
     <t>2026-03-20 13:29:00</t>
   </si>
   <si>
-    <t>54:51:19</t>
+    <t>55:28:01</t>
   </si>
   <si>
     <t>KA9999PO</t>
@@ -2697,7 +2697,7 @@
     <t>01:33:03</t>
   </si>
   <si>
-    <t>51:47:59</t>
+    <t>52:24:41</t>
   </si>
   <si>
     <t>KA5022PM</t>
@@ -2706,7 +2706,7 @@
     <t>2026-03-19 15:43:31</t>
   </si>
   <si>
-    <t>76:36:48</t>
+    <t>77:13:30</t>
   </si>
   <si>
     <t>9542KA</t>
@@ -2721,7 +2721,7 @@
     <t>2026-03-19 16:14:37</t>
   </si>
   <si>
-    <t>76:05:42</t>
+    <t>76:42:24</t>
   </si>
   <si>
     <t>2026-03-19 16:25:08</t>
@@ -2763,7 +2763,7 @@
     <t>00:53:41</t>
   </si>
   <si>
-    <t>03:01:17</t>
+    <t>03:37:59</t>
   </si>
   <si>
     <t>2026-03-22 17:19:37</t>
@@ -2781,7 +2781,7 @@
     <t>00:00:49</t>
   </si>
   <si>
-    <t>75:52:51</t>
+    <t>76:29:33</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA4027AT</t>
@@ -2805,7 +2805,7 @@
     <t>2026-03-19 16:49:38</t>
   </si>
   <si>
-    <t>75:30:41</t>
+    <t>76:07:23</t>
   </si>
   <si>
     <t>A4331PX</t>
@@ -2820,7 +2820,7 @@
     <t>2026-03-19 17:06:26</t>
   </si>
   <si>
-    <t>75:13:53</t>
+    <t>75:50:35</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: A8316MC</t>
@@ -2913,7 +2913,7 @@
     <t>2026-03-19 17:43:55</t>
   </si>
   <si>
-    <t>74:36:23</t>
+    <t>75:13:05</t>
   </si>
   <si>
     <t>AA4244A</t>
@@ -2928,7 +2928,7 @@
     <t>2026-03-19 18:12:05</t>
   </si>
   <si>
-    <t>74:08:14</t>
+    <t>74:44:56</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA3739P</t>
@@ -2946,7 +2946,7 @@
     <t>2026-03-19 19:36:46</t>
   </si>
   <si>
-    <t>72:43:33</t>
+    <t>73:20:15</t>
   </si>
   <si>
     <t>KA8564KK</t>
@@ -2961,7 +2961,7 @@
     <t>00:02:49</t>
   </si>
   <si>
-    <t>32:43:13</t>
+    <t>33:19:55</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA8564KK</t>
@@ -3000,7 +3000,7 @@
     <t>2026-03-20 08:35:59</t>
   </si>
   <si>
-    <t>59:44:20</t>
+    <t>60:21:02</t>
   </si>
   <si>
     <t>WIU90MG</t>
@@ -3012,7 +3012,7 @@
     <t>2026-03-20 08:49:30</t>
   </si>
   <si>
-    <t>59:30:49</t>
+    <t>60:07:31</t>
   </si>
   <si>
     <t>KA1596PC</t>
@@ -3036,7 +3036,7 @@
     <t>2026-03-20 09:04:09</t>
   </si>
   <si>
-    <t>59:16:10</t>
+    <t>59:52:52</t>
   </si>
   <si>
     <t>KA0887EI</t>
@@ -3075,7 +3075,7 @@
     <t>2026-03-20 18:15:27</t>
   </si>
   <si>
-    <t>50:04:51</t>
+    <t>50:41:33</t>
   </si>
   <si>
     <t>KA1010HT</t>
@@ -3084,7 +3084,7 @@
     <t>2026-03-20 09:11:33</t>
   </si>
   <si>
-    <t>59:08:46</t>
+    <t>59:45:28</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA1010HT</t>
@@ -3147,7 +3147,7 @@
     <t>2026-03-21 10:05:52</t>
   </si>
   <si>
-    <t>34:14:27</t>
+    <t>34:51:09</t>
   </si>
   <si>
     <t>LU598MC</t>
@@ -3201,7 +3201,7 @@
     <t>2026-03-20 12:32:25</t>
   </si>
   <si>
-    <t>55:47:54</t>
+    <t>56:24:36</t>
   </si>
   <si>
     <t>KA4573CT</t>
@@ -3234,7 +3234,7 @@
     <t>2026-03-20 13:53:45</t>
   </si>
   <si>
-    <t>54:26:34</t>
+    <t>55:03:16</t>
   </si>
   <si>
     <t>KA7781MC</t>
@@ -3264,7 +3264,7 @@
     <t>2026-03-20 11:11:11</t>
   </si>
   <si>
-    <t>57:09:08</t>
+    <t>57:45:50</t>
   </si>
   <si>
     <t>KI0001AE</t>
@@ -3297,7 +3297,7 @@
     <t>2026-03-20 13:24:29</t>
   </si>
   <si>
-    <t>54:55:50</t>
+    <t>55:32:32</t>
   </si>
   <si>
     <t>AE8866IB</t>
@@ -3333,7 +3333,7 @@
     <t>2026-03-20 14:54:16</t>
   </si>
   <si>
-    <t>53:26:03</t>
+    <t>54:02:45</t>
   </si>
   <si>
     <t>AE8866</t>
@@ -3348,7 +3348,7 @@
     <t>2026-03-20 10:28:38</t>
   </si>
   <si>
-    <t>57:51:41</t>
+    <t>58:28:23</t>
   </si>
   <si>
     <t>KV7121YK</t>
@@ -3363,7 +3363,7 @@
     <t>2026-03-20 10:38:26</t>
   </si>
   <si>
-    <t>57:41:53</t>
+    <t>58:18:35</t>
   </si>
   <si>
     <t>AA3000KP</t>
@@ -3399,7 +3399,7 @@
     <t>2026-03-20 16:58:36</t>
   </si>
   <si>
-    <t>51:21:43</t>
+    <t>51:58:25</t>
   </si>
   <si>
     <t>BK3978IC</t>
@@ -3408,7 +3408,7 @@
     <t>2026-03-20 11:08:18</t>
   </si>
   <si>
-    <t>57:12:01</t>
+    <t>57:48:43</t>
   </si>
   <si>
     <t>AX5300M</t>
@@ -3684,7 +3684,7 @@
     <t>2026-03-20 12:32:22</t>
   </si>
   <si>
-    <t>55:47:57</t>
+    <t>56:24:39</t>
   </si>
   <si>
     <t>AB7012KX</t>
@@ -3714,7 +3714,7 @@
     <t>2026-03-21 11:17:03</t>
   </si>
   <si>
-    <t>33:03:16</t>
+    <t>33:39:58</t>
   </si>
   <si>
     <t>LU595AG</t>
@@ -3747,7 +3747,7 @@
     <t>2026-03-20 15:41:45</t>
   </si>
   <si>
-    <t>52:38:34</t>
+    <t>53:15:16</t>
   </si>
   <si>
     <t>LU596NG</t>
@@ -3780,7 +3780,7 @@
     <t>2026-03-20 17:06:08</t>
   </si>
   <si>
-    <t>51:14:10</t>
+    <t>51:50:52</t>
   </si>
   <si>
     <t>KA2918PO</t>
@@ -3810,7 +3810,7 @@
     <t>2026-03-20 14:29:22</t>
   </si>
   <si>
-    <t>53:50:57</t>
+    <t>54:27:39</t>
   </si>
   <si>
     <t>KA2918P</t>
@@ -3873,7 +3873,7 @@
     <t>00:08:17</t>
   </si>
   <si>
-    <t>32:30:05</t>
+    <t>33:06:47</t>
   </si>
   <si>
     <t>2918PO</t>
@@ -3900,7 +3900,7 @@
     <t>2026-03-20 14:18:58</t>
   </si>
   <si>
-    <t>54:01:21</t>
+    <t>54:38:03</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: A9999PO</t>
@@ -3951,7 +3951,7 @@
     <t>2026-03-21 14:04:53</t>
   </si>
   <si>
-    <t>30:15:26</t>
+    <t>30:52:08</t>
   </si>
   <si>
     <t>2026-03-20 14:23:48</t>
@@ -3993,7 +3993,7 @@
     <t>02:53:09</t>
   </si>
   <si>
-    <t>03:10:46</t>
+    <t>03:47:28</t>
   </si>
   <si>
     <t>2026-03-22 17:10:11</t>
@@ -4023,7 +4023,7 @@
     <t>2026-03-20 14:36:20</t>
   </si>
   <si>
-    <t>53:43:59</t>
+    <t>54:20:41</t>
   </si>
   <si>
     <t>A0037CI</t>
@@ -4032,7 +4032,7 @@
     <t>2026-03-20 14:42:51</t>
   </si>
   <si>
-    <t>53:37:28</t>
+    <t>54:14:10</t>
   </si>
   <si>
     <t>KA0037CI</t>
@@ -4056,7 +4056,7 @@
     <t>2026-03-20 16:56:20</t>
   </si>
   <si>
-    <t>51:23:59</t>
+    <t>52:00:41</t>
   </si>
   <si>
     <t>AI3241MK</t>
@@ -4080,7 +4080,7 @@
     <t>2026-03-20 16:26:02</t>
   </si>
   <si>
-    <t>51:54:17</t>
+    <t>52:30:59</t>
   </si>
   <si>
     <t>KA0037CO</t>
@@ -4107,7 +4107,7 @@
     <t>2026-03-20 16:46:06</t>
   </si>
   <si>
-    <t>51:34:13</t>
+    <t>52:10:55</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: KA0037CO</t>
@@ -4140,7 +4140,7 @@
     <t>2026-03-20 17:24:20</t>
   </si>
   <si>
-    <t>50:55:59</t>
+    <t>51:32:41</t>
   </si>
   <si>
     <t>BH0081BX</t>
@@ -4161,7 +4161,7 @@
     <t>2026-03-20 15:21:32</t>
   </si>
   <si>
-    <t>52:58:47</t>
+    <t>53:35:29</t>
   </si>
   <si>
     <t>WN114KK</t>
@@ -4200,7 +4200,7 @@
     <t>2026-03-20 16:42:01</t>
   </si>
   <si>
-    <t>51:38:18</t>
+    <t>52:15:00</t>
   </si>
   <si>
     <t>KA5222CK</t>
@@ -4209,7 +4209,7 @@
     <t>2026-03-20 16:18:31</t>
   </si>
   <si>
-    <t>52:01:48</t>
+    <t>52:38:30</t>
   </si>
   <si>
     <t>AT0241BK</t>
@@ -4218,7 +4218,7 @@
     <t>2026-03-20 16:26:06</t>
   </si>
   <si>
-    <t>51:54:13</t>
+    <t>52:30:55</t>
   </si>
   <si>
     <t>AI566K</t>
@@ -4233,7 +4233,7 @@
     <t>2026-03-20 17:34:29</t>
   </si>
   <si>
-    <t>50:45:50</t>
+    <t>51:22:32</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: B6681BX</t>
@@ -4245,7 +4245,7 @@
     <t>2026-03-20 18:00:56</t>
   </si>
   <si>
-    <t>50:19:23</t>
+    <t>50:56:05</t>
   </si>
   <si>
     <t>KA7757AK</t>
@@ -4254,7 +4254,7 @@
     <t>2026-03-20 18:03:41</t>
   </si>
   <si>
-    <t>50:16:38</t>
+    <t>50:53:20</t>
   </si>
   <si>
     <t>KA7354PT</t>
@@ -4266,7 +4266,7 @@
     <t>2026-03-20 18:35:31</t>
   </si>
   <si>
-    <t>49:44:48</t>
+    <t>50:21:30</t>
   </si>
   <si>
     <t>KA7591B</t>
@@ -4275,7 +4275,7 @@
     <t>2026-03-20 18:50:31</t>
   </si>
   <si>
-    <t>49:29:48</t>
+    <t>50:06:30</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA7591B</t>
@@ -4287,7 +4287,7 @@
     <t>2026-03-20 19:51:20</t>
   </si>
   <si>
-    <t>48:28:59</t>
+    <t>49:05:41</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: KA5143OO</t>
@@ -4305,7 +4305,7 @@
     <t>00:06:36</t>
   </si>
   <si>
-    <t>35:41:32</t>
+    <t>36:18:14</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA1693TB</t>
@@ -4344,7 +4344,7 @@
     <t>2026-03-22 09:25:51</t>
   </si>
   <si>
-    <t>10:54:28</t>
+    <t>11:31:10</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: BX8177CB</t>
@@ -4380,7 +4380,7 @@
     <t>2026-03-21 11:06:23</t>
   </si>
   <si>
-    <t>33:13:56</t>
+    <t>33:50:38</t>
   </si>
   <si>
     <t>KA7354P</t>
@@ -4395,7 +4395,7 @@
     <t>2026-03-21 10:15:37</t>
   </si>
   <si>
-    <t>34:04:42</t>
+    <t>34:41:24</t>
   </si>
   <si>
     <t>No Post in within 15 minutes: KA7117XC</t>
@@ -4434,7 +4434,7 @@
     <t>2026-03-21 16:43:25</t>
   </si>
   <si>
-    <t>27:36:54</t>
+    <t>28:13:36</t>
   </si>
   <si>
     <t>AA5404TA</t>
@@ -4458,7 +4458,7 @@
     <t>2026-03-21 18:00:11</t>
   </si>
   <si>
-    <t>26:20:08</t>
+    <t>26:56:50</t>
   </si>
   <si>
     <t>7117YC</t>
@@ -4524,7 +4524,7 @@
     <t>2026-03-21 16:23:53</t>
   </si>
   <si>
-    <t>27:56:26</t>
+    <t>28:33:08</t>
   </si>
   <si>
     <t>BH7711AX</t>
@@ -4545,7 +4545,7 @@
     <t>2026-03-21 12:53:00</t>
   </si>
   <si>
-    <t>31:27:19</t>
+    <t>32:04:01</t>
   </si>
   <si>
     <t>AI0166TB</t>
@@ -4554,7 +4554,7 @@
     <t>2026-03-21 12:46:25</t>
   </si>
   <si>
-    <t>31:33:54</t>
+    <t>32:10:36</t>
   </si>
   <si>
     <t>KA8544KK</t>
@@ -4605,7 +4605,7 @@
     <t>2026-03-21 15:59:25</t>
   </si>
   <si>
-    <t>28:20:54</t>
+    <t>28:57:36</t>
   </si>
   <si>
     <t>KA241P</t>
@@ -4614,7 +4614,7 @@
     <t>2026-03-21 14:14:45</t>
   </si>
   <si>
-    <t>30:05:34</t>
+    <t>30:42:16</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: KA241P</t>
@@ -4641,7 +4641,7 @@
     <t>2026-03-21 14:56:56</t>
   </si>
   <si>
-    <t>29:23:23</t>
+    <t>30:00:05</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: AI1881YB</t>
@@ -4653,7 +4653,7 @@
     <t>2026-03-21 15:27:47</t>
   </si>
   <si>
-    <t>28:52:32</t>
+    <t>29:29:14</t>
   </si>
   <si>
     <t>KA7498PT</t>
@@ -4671,7 +4671,7 @@
     <t>2026-03-21 16:31:15</t>
   </si>
   <si>
-    <t>27:49:04</t>
+    <t>28:25:46</t>
   </si>
   <si>
     <t>KA8390PB</t>
@@ -4683,7 +4683,7 @@
     <t>2026-03-21 16:44:04</t>
   </si>
   <si>
-    <t>27:36:15</t>
+    <t>28:12:57</t>
   </si>
   <si>
     <t>KA3374KI</t>
@@ -4692,7 +4692,7 @@
     <t>2026-03-21 17:13:18</t>
   </si>
   <si>
-    <t>27:07:01</t>
+    <t>27:43:43</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: KA3374KI</t>
@@ -4752,7 +4752,7 @@
     <t>2026-03-22 14:10:08</t>
   </si>
   <si>
-    <t>06:10:11</t>
+    <t>06:46:53</t>
   </si>
   <si>
     <t>KP390P</t>
@@ -4761,7 +4761,7 @@
     <t>2026-03-22 14:10:11</t>
   </si>
   <si>
-    <t>06:10:08</t>
+    <t>06:46:50</t>
   </si>
   <si>
     <t>BK5282YA</t>
@@ -4770,7 +4770,7 @@
     <t>2026-03-22 16:05:37</t>
   </si>
   <si>
-    <t>04:14:42</t>
+    <t>04:51:24</t>
   </si>
   <si>
     <t>No Drive in (out) within 15 minutes: BK5282YA</t>
@@ -4782,7 +4782,7 @@
     <t>2026-03-22 16:48:50</t>
   </si>
   <si>
-    <t>03:31:29</t>
+    <t>04:08:11</t>
   </si>
   <si>
     <t>KA0350PI</t>
@@ -4791,7 +4791,7 @@
     <t>2026-03-22 17:10:22</t>
   </si>
   <si>
-    <t>03:09:57</t>
+    <t>03:46:39</t>
   </si>
   <si>
     <t>KA8390PA</t>
